--- a/procol test/fixtures/vendor-bulk-upload/VBU-111.xlsx
+++ b/procol test/fixtures/vendor-bulk-upload/VBU-111.xlsx
@@ -500,7 +500,7 @@
         <v>qa_vbu_{{stamp}}_111_1@example.com</v>
       </c>
       <c r="J4" t="str">
-        <v>QA{{stamp}}VVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVVV</v>
+        <v>{{vcode100}}</v>
       </c>
       <c r="V4" t="str">
         <v>No</v>
